--- a/data/trans_orig/P1427-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1427-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2012</t>
+          <t>Población con diagnóstico de cataratas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>9052</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24718</t>
+          <t>24886</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,82 +747,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>20973</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>13369</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>31970</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>36365</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>25435</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>49197</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>3,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>20973</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>13371</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>31783</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>36365</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>24018</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>50122</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>678751</t>
+          <t>678583</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>694958</t>
+          <t>694417</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,82 +860,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>96,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>676077</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>665080</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>683681</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>96,99%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,41%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>98,08%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1290</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1364154</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1351322</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1375084</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>96,49%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>631</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>676077</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>665267</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>683679</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,44%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1290</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1364154</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1350397</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1376501</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12394</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34039</t>
+          <t>33356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17920</t>
+          <t>18296</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40385</t>
+          <t>40219</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35314</t>
+          <t>36008</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67724</t>
+          <t>66438</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>983908</t>
+          <t>984591</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1005553</t>
+          <t>1005977</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>988588</t>
+          <t>988754</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1011053</t>
+          <t>1010677</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1979197</t>
+          <t>1980483</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2011607</t>
+          <t>2010913</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18776</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28660</t>
+          <t>27751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>18710</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>41050</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>738847</t>
+          <t>739156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>752443</t>
+          <t>752532</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>748514</t>
+          <t>749423</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>766969</t>
+          <t>767482</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1495856</t>
+          <t>1493747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1516935</t>
+          <t>1516087</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31686</t>
+          <t>33398</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19101</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41143</t>
+          <t>41807</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36677</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66001</t>
+          <t>67897</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>916053</t>
+          <t>914341</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>934851</t>
+          <t>934814</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1010758</t>
+          <t>1010094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1032800</t>
+          <t>1032173</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1933639</t>
+          <t>1931743</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1962963</t>
+          <t>1963055</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52410</t>
+          <t>53484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87241</t>
+          <t>86156</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75468</t>
+          <t>75593</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116097</t>
+          <t>116739</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>135571</t>
+          <t>136186</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>188428</t>
+          <t>188561</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3339538</t>
+          <t>3340623</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3374369</t>
+          <t>3373295</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3439001</t>
+          <t>3438359</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3479630</t>
+          <t>3479505</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6793449</t>
+          <t>6793316</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6846306</t>
+          <t>6845691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2016</t>
+          <t>Población con diagnóstico de cataratas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4319</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16818</t>
+          <t>16721</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25994</t>
+          <t>25208</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36923</t>
+          <t>38045</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>657982</t>
+          <t>658079</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>670481</t>
+          <t>670505</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>646845</t>
+          <t>647631</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663342</t>
+          <t>663893</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1310716</t>
+          <t>1309594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1331260</t>
+          <t>1330566</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>14484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10185</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28108</t>
+          <t>27829</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17070</t>
+          <t>16327</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36846</t>
+          <t>35931</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1007425</t>
+          <t>1007947</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1018749</t>
+          <t>1018862</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1014805</t>
+          <t>1015084</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1032728</t>
+          <t>1032969</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2028498</t>
+          <t>2029413</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2048274</t>
+          <t>2049017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14135</t>
+          <t>15902</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9127</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25597</t>
+          <t>26698</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>14459</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35537</t>
+          <t>34246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>745417</t>
+          <t>743650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>756575</t>
+          <t>756083</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>759414</t>
+          <t>758313</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>775884</t>
+          <t>776117</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1509026</t>
+          <t>1510317</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1530107</t>
+          <t>1530104</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19491</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20346</t>
+          <t>21142</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43376</t>
+          <t>45476</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30011</t>
+          <t>28791</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56861</t>
+          <t>56119</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>918076</t>
+          <t>918158</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>931236</t>
+          <t>932066</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1000403</t>
+          <t>998303</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1023433</t>
+          <t>1022637</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1924485</t>
+          <t>1925227</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1951335</t>
+          <t>1952555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>25073</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48148</t>
+          <t>48345</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61224</t>
+          <t>63420</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100147</t>
+          <t>99565</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93749</t>
+          <t>93876</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>137383</t>
+          <t>139477</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3346202</t>
+          <t>3346005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3368859</t>
+          <t>3369277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3444395</t>
+          <t>3444977</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3483318</t>
+          <t>3481122</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6801509</t>
+          <t>6799415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6845143</t>
+          <t>6845016</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cataratas en 2023</t>
+          <t>Población con diagnóstico de cataratas en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21572</t>
+          <t>21763</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37114</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>36117</t>
+          <t>37344</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53147</t>
+          <t>53535</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62753</t>
+          <t>62496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>87287</t>
+          <t>86132</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4711,12 +4711,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>598327</t>
+          <t>597042</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>613869</t>
+          <t>613678</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>621592</t>
+          <t>621204</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>638622</t>
+          <t>637395</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1222894</t>
+          <t>1224049</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1247428</t>
+          <t>1247685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -4969,12 +4969,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>14241</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43291</t>
+          <t>42922</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23556</t>
+          <t>23302</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39027</t>
+          <t>39327</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39814</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76253</t>
+          <t>75405</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1149573</t>
+          <t>1149942</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1177656</t>
+          <t>1178623</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>917977</t>
+          <t>917677</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>933448</t>
+          <t>933702</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2073615</t>
+          <t>2074463</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2110054</t>
+          <t>2111408</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -5312,12 +5312,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>10067</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25526</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5327,12 +5327,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16026</t>
+          <t>14781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47116</t>
+          <t>46208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5362,12 +5362,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31151</t>
+          <t>29182</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63121</t>
+          <t>63255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>674514</t>
+          <t>675694</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>690044</t>
+          <t>689973</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>885603</t>
+          <t>886511</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>916693</t>
+          <t>917938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1569638</t>
+          <t>1569504</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1601608</t>
+          <t>1603577</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22238</t>
+          <t>21444</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40301</t>
+          <t>40272</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5670,7 +5670,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35966</t>
+          <t>36899</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71944</t>
+          <t>68000</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63094</t>
+          <t>62409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>100713</t>
+          <t>98829</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -5768,12 +5768,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>886530</t>
+          <t>886559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>904593</t>
+          <t>905387</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5788,7 +5788,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1019970</t>
+          <t>1023914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1055948</t>
+          <t>1055015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1918032</t>
+          <t>1919916</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1955651</t>
+          <t>1956336</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5853,12 +5853,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,91%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82159</t>
+          <t>80934</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125938</t>
+          <t>125683</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>126816</t>
+          <t>124658</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181219</t>
+          <t>181666</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>228171</t>
+          <t>226231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>296101</t>
+          <t>294663</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -6111,12 +6111,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3329238</t>
+          <t>3329493</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3373017</t>
+          <t>3374242</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3475158</t>
+          <t>3474711</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3529561</t>
+          <t>3531719</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6815452</t>
+          <t>6816890</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6883382</t>
+          <t>6885322</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6196,12 +6196,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1427-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1427-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9052</t>
+          <t>9534</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24886</t>
+          <t>25746</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31970</t>
+          <t>32184</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25435</t>
+          <t>25855</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49197</t>
+          <t>49751</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>678583</t>
+          <t>677723</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>694417</t>
+          <t>693935</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>665080</t>
+          <t>664866</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>683681</t>
+          <t>683458</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1351322</t>
+          <t>1350768</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1375084</t>
+          <t>1374664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>12922</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33356</t>
+          <t>35646</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18296</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40219</t>
+          <t>40452</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36008</t>
+          <t>35834</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66438</t>
+          <t>65553</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>984591</t>
+          <t>982301</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1005977</t>
+          <t>1005025</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>988754</t>
+          <t>988521</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1010677</t>
+          <t>1011426</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1980483</t>
+          <t>1981368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2010913</t>
+          <t>2011087</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5091</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18467</t>
+          <t>19483</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27751</t>
+          <t>28192</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>18710</t>
+          <t>17792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41050</t>
+          <t>40688</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739156</t>
+          <t>738140</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>752532</t>
+          <t>752482</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>749423</t>
+          <t>748982</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>767482</t>
+          <t>767145</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1493747</t>
+          <t>1494109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1516087</t>
+          <t>1517005</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12925</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33398</t>
+          <t>34154</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19728</t>
+          <t>19203</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41807</t>
+          <t>41182</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>36112</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67897</t>
+          <t>64950</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>914341</t>
+          <t>913585</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>934814</t>
+          <t>934363</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1010094</t>
+          <t>1010719</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1032173</t>
+          <t>1032698</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1931743</t>
+          <t>1934690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1963055</t>
+          <t>1963528</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53484</t>
+          <t>52928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86156</t>
+          <t>88371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75593</t>
+          <t>76098</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116739</t>
+          <t>117673</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>136186</t>
+          <t>136074</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>188561</t>
+          <t>187911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3340623</t>
+          <t>3338408</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3373295</t>
+          <t>3373851</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3438359</t>
+          <t>3437425</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3479505</t>
+          <t>3479000</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6793316</t>
+          <t>6793966</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6845691</t>
+          <t>6845803</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4295</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16721</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25208</t>
+          <t>26427</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17073</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38045</t>
+          <t>37688</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>658079</t>
+          <t>658102</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>670505</t>
+          <t>669990</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>647631</t>
+          <t>646412</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663893</t>
+          <t>663015</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1309594</t>
+          <t>1309951</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1330566</t>
+          <t>1331151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27829</t>
+          <t>27964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16327</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35931</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1007947</t>
+          <t>1007332</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1018862</t>
+          <t>1018790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1015084</t>
+          <t>1014949</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1032969</t>
+          <t>1032956</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2029413</t>
+          <t>2029341</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2049017</t>
+          <t>2048823</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15902</t>
+          <t>15043</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26698</t>
+          <t>26469</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>15367</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34246</t>
+          <t>36116</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>743650</t>
+          <t>744509</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>756083</t>
+          <t>756624</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>758313</t>
+          <t>758542</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>776117</t>
+          <t>776325</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1510317</t>
+          <t>1508447</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1530104</t>
+          <t>1529196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19409</t>
+          <t>19207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>20515</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45476</t>
+          <t>44112</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3778,12 +3778,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28791</t>
+          <t>30415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56119</t>
+          <t>57214</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>918158</t>
+          <t>918360</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932066</t>
+          <t>931563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3856,12 +3856,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>998303</t>
+          <t>999667</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1022637</t>
+          <t>1023264</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3891,12 +3891,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1925227</t>
+          <t>1924132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1952555</t>
+          <t>1950931</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25073</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48345</t>
+          <t>48016</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63420</t>
+          <t>63030</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99565</t>
+          <t>100160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93876</t>
+          <t>96676</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139477</t>
+          <t>141206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3346005</t>
+          <t>3346334</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3369277</t>
+          <t>3368858</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3444977</t>
+          <t>3444382</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3481122</t>
+          <t>3481512</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6799415</t>
+          <t>6797686</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6845016</t>
+          <t>6842216</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4249,12 +4249,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,61%</t>
         </is>
       </c>
     </row>
@@ -4621,32 +4621,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29081</t>
+          <t>29237</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21763</t>
+          <t>22252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38399</t>
+          <t>38252</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4656,32 +4656,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44598</t>
+          <t>46032</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37344</t>
+          <t>37416</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53535</t>
+          <t>54356</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4691,32 +4691,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>73679</t>
+          <t>75269</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>62496</t>
+          <t>63175</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86132</t>
+          <t>88044</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>606360</t>
+          <t>661473</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>597042</t>
+          <t>652458</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>613678</t>
+          <t>668458</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>630141</t>
+          <t>686001</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>621204</t>
+          <t>677677</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>637395</t>
+          <t>694617</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1236502</t>
+          <t>1347473</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1224049</t>
+          <t>1334698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1247685</t>
+          <t>1359567</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,56%</t>
         </is>
       </c>
     </row>
@@ -4847,17 +4847,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4882,17 +4882,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>674739</t>
+          <t>732033</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>674739</t>
+          <t>732033</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>674739</t>
+          <t>732033</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310181</t>
+          <t>1422742</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310181</t>
+          <t>1422742</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310181</t>
+          <t>1422742</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4964,102 +4964,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>30291</t>
+          <t>32096</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14241</t>
+          <t>23797</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42922</t>
+          <t>45173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>3,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>33527</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>26257</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>42771</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>65623</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>53747</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>78977</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>3,1%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>2,54%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>30742</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>23302</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>39327</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>61033</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>38460</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>75405</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -5077,102 +5077,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1162573</t>
+          <t>1016821</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1149942</t>
+          <t>1003744</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1178623</t>
+          <t>1025120</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>96,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1036202</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1026958</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1043472</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,0%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2365</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2053023</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2039669</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2064899</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>96,9%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>96,27%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>97,46%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>926262</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>917677</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>933702</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>96,79%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>95,89%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>97,57%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2365</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2088835</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>2074463</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2111408</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5190,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>957004</t>
+          <t>1069729</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>957004</t>
+          <t>1069729</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>957004</t>
+          <t>1069729</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5260,17 +5260,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149868</t>
+          <t>2118646</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149868</t>
+          <t>2118646</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149868</t>
+          <t>2118646</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5307,32 +5307,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16230</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>11182</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24346</t>
+          <t>27091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5342,32 +5342,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>32809</t>
+          <t>38296</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14781</t>
+          <t>28549</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46208</t>
+          <t>48383</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>4,72%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>3,52%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5377,32 +5377,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49039</t>
+          <t>56148</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29182</t>
+          <t>44396</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63255</t>
+          <t>70303</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>683810</t>
+          <t>780200</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>675694</t>
+          <t>770962</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>689973</t>
+          <t>786871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5455,34 +5455,34 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>899910</t>
+          <t>773239</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>886511</t>
+          <t>763152</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>917938</t>
+          <t>782986</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t>95,28%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>94,04%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>96,48%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1639</t>
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1583720</t>
+          <t>1553439</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1569504</t>
+          <t>1539284</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1603577</t>
+          <t>1565191</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -5533,17 +5533,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>700040</t>
+          <t>798053</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>700040</t>
+          <t>798053</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>700040</t>
+          <t>798053</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932719</t>
+          <t>811535</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932719</t>
+          <t>811535</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932719</t>
+          <t>811535</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5603,17 +5603,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1632759</t>
+          <t>1609587</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1632759</t>
+          <t>1609587</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1632759</t>
+          <t>1609587</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29842</t>
+          <t>30434</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21444</t>
+          <t>23074</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40272</t>
+          <t>40576</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>48642</t>
+          <t>47573</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36899</t>
+          <t>38120</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68000</t>
+          <t>59735</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>78485</t>
+          <t>78007</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62409</t>
+          <t>64806</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>98829</t>
+          <t>93168</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>896989</t>
+          <t>959628</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>886559</t>
+          <t>949486</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>905387</t>
+          <t>966988</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1043272</t>
+          <t>1070061</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1023914</t>
+          <t>1057899</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1055015</t>
+          <t>1079514</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1940260</t>
+          <t>2029689</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1919916</t>
+          <t>2014528</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1956336</t>
+          <t>2042890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -5876,17 +5876,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5911,17 +5911,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5946,17 +5946,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018745</t>
+          <t>2107696</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018745</t>
+          <t>2107696</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018745</t>
+          <t>2107696</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>105444</t>
+          <t>109619</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80934</t>
+          <t>92165</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125683</t>
+          <t>128153</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>156792</t>
+          <t>165427</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>124658</t>
+          <t>146671</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181666</t>
+          <t>186357</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>262236</t>
+          <t>275046</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>226231</t>
+          <t>250908</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>294663</t>
+          <t>304092</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3349732</t>
+          <t>3418123</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3329493</t>
+          <t>3399589</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3374242</t>
+          <t>3435577</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3499585</t>
+          <t>3565504</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3474711</t>
+          <t>3544574</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3531719</t>
+          <t>3584260</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6849317</t>
+          <t>6983626</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6816890</t>
+          <t>6954580</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6885322</t>
+          <t>7007764</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -6219,17 +6219,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3455176</t>
+          <t>3527742</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3455176</t>
+          <t>3527742</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3455176</t>
+          <t>3527742</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6254,17 +6254,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3656377</t>
+          <t>3730931</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3656377</t>
+          <t>3730931</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3656377</t>
+          <t>3730931</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7111553</t>
+          <t>7258672</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7111553</t>
+          <t>7258672</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7111553</t>
+          <t>7258672</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
